--- a/app/assets/images/CHEDP.GB.2025.5403171.xlsx
+++ b/app/assets/images/CHEDP.GB.2025.5403171.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Personal/Documents/GitHub/btms-prototype/app/assets/images/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC27E6AB-B706-C24B-B169-AF0E1DDD1D83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82B87362-B3BF-A84D-8AEB-0B27CB02B539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14380" xr2:uid="{4240C3A9-E378-4CEC-8258-EAA0CD32FEE7}"/>
   </bookViews>
@@ -698,7 +698,7 @@
       <c r="I6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J6" s="1" t="s">
+      <c r="J6" s="5" t="s">
         <v>7</v>
       </c>
       <c r="K6" s="5" t="s">
@@ -736,7 +736,7 @@
       <c r="I7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="5" t="s">
         <v>10</v>
       </c>
       <c r="K7" s="5" t="s">
@@ -774,7 +774,7 @@
       <c r="I8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="1" t="s">
+      <c r="J8" s="5" t="s">
         <v>7</v>
       </c>
       <c r="K8" s="5" t="s">
@@ -812,7 +812,7 @@
       <c r="I9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="1" t="s">
+      <c r="J9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="K9" s="5" t="s">
